--- a/data/trans_orig/IP2005-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2005-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>108348</t>
+          <t>108254</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>118863</t>
+          <t>118805</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>121077</t>
+          <t>120208</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>131859</t>
+          <t>131691</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>233728</t>
+          <t>233518</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>248724</t>
+          <t>248048</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17920</t>
+          <t>18014</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18511</t>
+          <t>19380</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17132</t>
+          <t>17808</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32128</t>
+          <t>32338</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>153920</t>
+          <t>153446</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>168750</t>
+          <t>167795</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>159954</t>
+          <t>159779</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>177539</t>
+          <t>176650</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>319436</t>
+          <t>317914</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>341489</t>
+          <t>340988</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,59%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17034</t>
+          <t>17989</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31864</t>
+          <t>32338</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25972</t>
+          <t>26861</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43557</t>
+          <t>43732</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47806</t>
+          <t>48307</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69859</t>
+          <t>71381</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110499</t>
+          <t>109945</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120319</t>
+          <t>120684</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>123964</t>
+          <t>124110</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133809</t>
+          <t>133886</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>238176</t>
+          <t>238068</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>252159</t>
+          <t>252030</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,16%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17809</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15378</t>
+          <t>15232</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15490</t>
+          <t>15619</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29473</t>
+          <t>29581</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>165833</t>
+          <t>165161</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>180674</t>
+          <t>180591</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>168656</t>
+          <t>168147</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>182475</t>
+          <t>182431</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>338004</t>
+          <t>338351</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>358267</t>
+          <t>359904</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15003</t>
+          <t>15086</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29844</t>
+          <t>30516</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13350</t>
+          <t>13394</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27169</t>
+          <t>27678</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33235</t>
+          <t>31598</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53498</t>
+          <t>53151</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>552531</t>
+          <t>550920</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>576424</t>
+          <t>577113</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>588262</t>
+          <t>588853</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>613949</t>
+          <t>615466</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1148769</t>
+          <t>1147811</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1184449</t>
+          <t>1183551</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,05%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59614</t>
+          <t>58925</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83507</t>
+          <t>85118</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64316</t>
+          <t>62799</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90003</t>
+          <t>89412</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>129854</t>
+          <t>130752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>165534</t>
+          <t>166492</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112179</t>
+          <t>112186</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>124224</t>
+          <t>124622</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>118313</t>
+          <t>118317</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>131057</t>
+          <t>131216</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>236112</t>
+          <t>234788</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>252681</t>
+          <t>252302</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8944</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20989</t>
+          <t>20982</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>9756</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>22655</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21459</t>
+          <t>21838</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38028</t>
+          <t>39352</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>163452</t>
+          <t>163876</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>176553</t>
+          <t>177143</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>183032</t>
+          <t>182144</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>197581</t>
+          <t>196468</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>351002</t>
+          <t>350203</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>370453</t>
+          <t>369786</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14256</t>
+          <t>13666</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27357</t>
+          <t>26933</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>15617</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29053</t>
+          <t>29941</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32441</t>
+          <t>33108</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51892</t>
+          <t>52691</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124700</t>
+          <t>124433</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>136107</t>
+          <t>136030</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131408</t>
+          <t>131853</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142817</t>
+          <t>143202</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>259151</t>
+          <t>259794</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>274991</t>
+          <t>275606</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,08%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19958</t>
+          <t>20225</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20027</t>
+          <t>19582</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21102</t>
+          <t>20487</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36942</t>
+          <t>36299</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>167776</t>
+          <t>168122</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181801</t>
+          <t>181914</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>174460</t>
+          <t>174380</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>186966</t>
+          <t>186968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>348121</t>
+          <t>347214</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>366099</t>
+          <t>366429</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9878</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23903</t>
+          <t>23557</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20641</t>
+          <t>20721</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20681</t>
+          <t>20351</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38659</t>
+          <t>39566</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>582311</t>
+          <t>582533</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>608271</t>
+          <t>607939</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>622104</t>
+          <t>622114</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>647771</t>
+          <t>647513</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1212613</t>
+          <t>1213770</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1249917</t>
+          <t>1248925</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52043</t>
+          <t>52375</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78003</t>
+          <t>77781</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51822</t>
+          <t>52080</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77489</t>
+          <t>77479</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>109990</t>
+          <t>110982</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>147294</t>
+          <t>146137</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109985</t>
+          <t>109723</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119985</t>
+          <t>120071</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>117305</t>
+          <t>117739</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>129169</t>
+          <t>129344</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>232154</t>
+          <t>231559</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>247737</t>
+          <t>247078</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14067</t>
+          <t>14329</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21105</t>
+          <t>20671</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14725</t>
+          <t>15384</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30308</t>
+          <t>30903</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>172946</t>
+          <t>172900</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>184840</t>
+          <t>184584</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>187031</t>
+          <t>187657</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>199933</t>
+          <t>199644</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>364522</t>
+          <t>364328</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>381589</t>
+          <t>381174</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>9279</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20917</t>
+          <t>20963</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10100</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23002</t>
+          <t>22376</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22307</t>
+          <t>22722</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39374</t>
+          <t>39568</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>133036</t>
+          <t>133030</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>141761</t>
+          <t>141184</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>136598</t>
+          <t>135571</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149399</t>
+          <t>149372</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>271529</t>
+          <t>272301</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>287917</t>
+          <t>287812</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12942</t>
+          <t>12948</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9629</t>
+          <t>9656</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22430</t>
+          <t>23457</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17089</t>
+          <t>17194</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33477</t>
+          <t>32705</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>170171</t>
+          <t>170319</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>183234</t>
+          <t>183452</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>167284</t>
+          <t>165336</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>180330</t>
+          <t>179926</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>342629</t>
+          <t>341630</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>360963</t>
+          <t>360183</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9249</t>
+          <t>9031</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22312</t>
+          <t>22164</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10351</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23397</t>
+          <t>25345</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22200</t>
+          <t>22980</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40534</t>
+          <t>41533</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>600248</t>
+          <t>600600</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>621850</t>
+          <t>621485</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>622476</t>
+          <t>623220</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>648463</t>
+          <t>648223</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1231855</t>
+          <t>1229970</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1266165</t>
+          <t>1263683</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34526</t>
+          <t>34891</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56128</t>
+          <t>55776</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49689</t>
+          <t>49929</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75676</t>
+          <t>74932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>88362</t>
+          <t>90844</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>122672</t>
+          <t>124557</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96780</t>
+          <t>97320</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>108345</t>
+          <t>108226</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114119</t>
+          <t>114855</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>129135</t>
+          <t>129466</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>215980</t>
+          <t>216397</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>234266</t>
+          <t>234834</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18735</t>
+          <t>18195</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22638</t>
+          <t>21902</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18007</t>
+          <t>17439</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36293</t>
+          <t>35876</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>167000</t>
+          <t>166911</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>178059</t>
+          <t>178384</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>210214</t>
+          <t>210549</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229607</t>
+          <t>229598</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>383104</t>
+          <t>382917</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>404975</t>
+          <t>405406</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19898</t>
+          <t>19987</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>18838</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38222</t>
+          <t>37887</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30358</t>
+          <t>29927</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52229</t>
+          <t>52416</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>160994</t>
+          <t>159850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>177311</t>
+          <t>176982</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>154010</t>
+          <t>153710</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>169898</t>
+          <t>169589</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>320141</t>
+          <t>319230</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>343273</t>
+          <t>342601</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,17%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>11005</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26993</t>
+          <t>28137</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13805</t>
+          <t>14114</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29693</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28417</t>
+          <t>29089</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51549</t>
+          <t>52460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120801</t>
+          <t>121252</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>138778</t>
+          <t>139602</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>138465</t>
+          <t>139765</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>156977</t>
+          <t>156770</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>266091</t>
+          <t>265955</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>291602</t>
+          <t>292670</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>85,08%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27338</t>
+          <t>26514</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45315</t>
+          <t>44864</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20886</t>
+          <t>21093</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39398</t>
+          <t>38098</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>52377</t>
+          <t>51309</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>77888</t>
+          <t>78024</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>561306</t>
+          <t>561769</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>591304</t>
+          <t>591434</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>638014</t>
+          <t>638033</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>673197</t>
+          <t>672062</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1209241</t>
+          <t>1212458</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1254989</t>
+          <t>1257706</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,63%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65212</t>
+          <t>65082</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95210</t>
+          <t>94747</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73562</t>
+          <t>74697</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>108745</t>
+          <t>108726</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>148286</t>
+          <t>145569</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>194034</t>
+          <t>190817</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2005-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2005-Habitat-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si sus dientes estan sanos en 2007 (tasa de respuesta: 98,55%)</t>
+          <t>Menores según si sus dientes están sanos en 2007 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>127283</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>121278</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>131697</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>91,18%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>86,88%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>94,35%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>114446</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>108254</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>118805</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>108354</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>118971</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>90,64%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>85,73%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>94,09%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>127283</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>120208</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>131691</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>91,18%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>233518</t>
+          <t>233795</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>248048</t>
+          <t>248538</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12305</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7891</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18310</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>13,12%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>11822</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7463</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18014</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7297</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17914</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>9,36%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>14,27%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12305</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7897</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>19380</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17808</t>
+          <t>17318</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32338</t>
+          <t>32061</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>139588</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>139588</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>139588</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>126268</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>126268</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>126268</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>139588</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>139588</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>139588</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1071,67 +1071,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>169093</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>160377</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>176786</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>83,09%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>78,81%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>86,87%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>161195</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>153446</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>167795</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>153610</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>167963</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>86,76%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>82,59%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>90,32%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>169093</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>159779</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>176650</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>83,09%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>317914</t>
+          <t>317818</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>340988</t>
+          <t>340727</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>34418</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>26725</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>43134</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>16,91%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>13,13%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>21,19%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>24589</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17989</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>32338</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>17821</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>32174</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>13,24%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,68%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>17,41%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>34418</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>26861</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>43732</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>16,91%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48307</t>
+          <t>48568</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71381</t>
+          <t>71477</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>203511</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>203511</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>203511</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>297</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185784</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185784</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185784</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>203511</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>203511</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>203511</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>129849</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>123877</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>133902</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>93,19%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>88,9%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>96,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>115853</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>109945</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>120684</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>110343</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>120227</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>90,29%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>85,69%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>94,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>129849</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>124110</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>133886</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>93,19%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>238068</t>
+          <t>238225</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>252030</t>
+          <t>251839</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9493</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5440</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>15465</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6,81%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>12455</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7624</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>18363</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>8081</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>17965</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>9,71%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>14,31%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>9493</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>5456</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>15232</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15619</t>
+          <t>15810</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29581</t>
+          <t>29424</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139342</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>139342</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>139342</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>128308</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>128308</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>128308</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139342</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>139342</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>139342</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>176221</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>168327</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>182353</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>89,99%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>85,96%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>93,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>173547</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>165161</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>180591</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>165015</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>180207</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>88,69%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>84,4%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>92,29%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>176221</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>168147</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>182431</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>89,99%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>338351</t>
+          <t>337751</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>359904</t>
+          <t>359712</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,88%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19604</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13472</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>27498</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6,88%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>14,04%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>22130</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>15086</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>30516</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>15470</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>30662</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>11,31%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,71%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,6%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>19604</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>13394</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>27678</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31598</t>
+          <t>31790</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53151</t>
+          <t>53751</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>195825</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>195825</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>195825</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>195677</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>195677</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>195677</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>195825</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>195825</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>195825</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>602445</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>588001</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>615775</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>88,82%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>86,69%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>90,79%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>842</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>565042</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>550920</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>577113</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>552078</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>577011</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>88,84%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>86,62%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>90,74%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>602445</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>588853</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>615466</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>88,82%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1147811</t>
+          <t>1151246</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1183551</t>
+          <t>1186030</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>75820</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>62490</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>90264</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>11,18%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>13,31%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>70996</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>58925</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>85118</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>59027</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>83960</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>11,16%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>13,38%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>75820</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>62799</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>89412</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>11,18%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>130752</t>
+          <t>128273</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>166492</t>
+          <t>163057</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>678265</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>678265</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>678265</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>950</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>636038</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>636038</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>636038</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>678265</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>678265</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>678265</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si sus dientes estan sanos en 2012 (tasa de respuesta: 99,54%)</t>
+          <t>Menores según si sus dientes están sanos en 2012 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>125429</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>118564</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>131411</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>88,97%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>84,1%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>93,22%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>119248</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>112186</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>124622</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>112224</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>124339</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>89,55%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84,24%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>93,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>125429</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>118317</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>131216</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>88,97%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>234788</t>
+          <t>234882</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>252302</t>
+          <t>252579</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15543</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9561</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22408</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11,03%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,78%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>15,9%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>13920</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8546</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>20982</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8829</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>20944</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>10,45%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>15,76%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>15543</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9756</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22655</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>11,03%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21838</t>
+          <t>21561</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39352</t>
+          <t>39258</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>140972</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>140972</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>140972</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133168</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133168</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133168</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>140972</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>140972</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>140972</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>190658</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>183144</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>197079</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>89,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>86,35%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>92,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>170702</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>163876</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>177143</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>162946</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>176621</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>89,46%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>85,88%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>92,84%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>190658</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>182144</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>196468</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>89,9%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>350203</t>
+          <t>350187</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>369786</t>
+          <t>370641</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21427</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15006</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>28941</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>10,1%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>13,65%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>20107</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13666</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>26933</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>14188</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>27863</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>10,54%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14,12%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>21427</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>15617</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>29941</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>10,1%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33108</t>
+          <t>32253</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52691</t>
+          <t>52707</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212085</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212085</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212085</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>295</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>190809</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>190809</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>190809</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212085</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212085</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212085</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>137856</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>131447</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>142598</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>91,03%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>86,8%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>94,16%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>130671</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>124433</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>136030</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>124075</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>135420</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>90,33%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>86,02%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>94,04%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>137856</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>131853</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>143202</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>91,03%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>259794</t>
+          <t>259487</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>275606</t>
+          <t>275890</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -3474,67 +3474,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>13579</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8837</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>19988</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8,97%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>13,2%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>13987</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8628</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>20225</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>9238</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>20583</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>9,67%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>13,98%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>13579</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>8233</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>19582</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20487</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36299</t>
+          <t>36606</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>151435</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>151435</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>151435</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>144658</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>144658</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>144658</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>151435</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>151435</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>151435</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>182032</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>175667</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>187852</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>93,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>90,04%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>96,28%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>175868</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>168122</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>181914</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>167570</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>181293</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>91,75%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>87,71%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>94,91%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>182032</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>174380</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>186968</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>93,3%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>347214</t>
+          <t>348062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>366429</t>
+          <t>365993</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13069</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7249</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>19434</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>15811</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9765</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>23557</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>10386</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>24109</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>8,25%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>13069</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>8133</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>20721</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>6,7%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20351</t>
+          <t>20787</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39566</t>
+          <t>38718</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>195101</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>195101</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>195101</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>250</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>191679</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>191679</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>191679</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>195101</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>195101</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>195101</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>635974</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>621627</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>647096</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>90,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>88,86%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>92,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>861</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>596489</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>582533</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>607939</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>583154</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>609046</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>90,33%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>88,22%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>92,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>635974</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>622114</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>647513</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>90,91%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1213770</t>
+          <t>1213678</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1248925</t>
+          <t>1247739</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,75%</t>
         </is>
       </c>
     </row>
@@ -4160,67 +4160,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>63619</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>52497</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>77966</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>9,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>11,14%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>63825</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>52375</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>77781</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>51268</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>77160</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>9,67%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>11,78%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>63619</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>52080</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>77479</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>9,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>110982</t>
+          <t>112168</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>146137</t>
+          <t>146229</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699593</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699593</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699593</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>951</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>660314</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>660314</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>660314</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>699593</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>699593</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>699593</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si sus dientes estan sanos en 2016 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según si sus dientes están sanos en 2016 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>124362</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>117016</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>129595</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>89,85%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>84,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>93,63%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>116194</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>109723</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>120071</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>110194</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>119975</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>93,67%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>88,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>96,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>124362</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>117739</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>129344</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>89,85%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>231559</t>
+          <t>232036</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>247078</t>
+          <t>248018</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14048</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8815</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21394</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10,15%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,37%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>15,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>7858</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3981</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14329</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4077</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>13858</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>6,33%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>11,55%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>14048</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9066</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20671</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15384</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30903</t>
+          <t>30426</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>138410</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>138410</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>138410</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>124052</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>124052</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>124052</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>138410</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>138410</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>138410</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>194231</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>187540</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>199474</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>92,48%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>89,29%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>94,97%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>289</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>179840</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>172900</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>184584</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>173618</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>185145</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>92,77%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>89,19%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>95,21%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>194231</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>187657</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>199644</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>92,48%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>364328</t>
+          <t>362686</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>381174</t>
+          <t>381272</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15802</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10559</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>22493</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7,52%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>10,71%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>14023</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9279</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20963</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>8718</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>20245</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>7,23%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,81%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>15802</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>10389</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>22376</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>7,52%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22722</t>
+          <t>22624</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39568</t>
+          <t>41210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>210033</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>210033</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>210033</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>193863</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>193863</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>193863</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>210033</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>210033</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>210033</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>143400</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>136006</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>149261</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>90,17%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>85,52%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>93,86%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>137911</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>133030</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>141184</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>132899</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>141388</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>94,47%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>91,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>96,72%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>143400</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>135571</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>149372</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>90,17%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>272301</t>
+          <t>272942</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>287812</t>
+          <t>287591</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15628</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9767</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23022</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>14,48%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>8067</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4794</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12948</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4590</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>13079</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>5,53%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>8,87%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>15628</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>9656</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>23457</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17194</t>
+          <t>17415</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32705</t>
+          <t>32064</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>159028</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>159028</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>159028</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>145978</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>145978</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>145978</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>159028</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>159028</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>159028</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>174618</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>167060</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>180656</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>91,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>87,61%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>94,74%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>177992</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>170319</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>183452</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>170908</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>183405</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>92,47%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>88,49%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>95,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>174618</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>165336</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>179926</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>91,58%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>341630</t>
+          <t>342106</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>360183</t>
+          <t>361258</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,28%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16063</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10025</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23621</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8,42%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>12,39%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>14491</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9031</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>22164</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>9078</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>21575</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>7,53%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>11,51%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>16063</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>10755</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>25345</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22980</t>
+          <t>21905</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41533</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>190681</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>190681</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>190681</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>192483</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>192483</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>192483</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>190681</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>190681</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>190681</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>636612</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>623795</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>648383</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>91,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>89,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>92,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>918</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>611937</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>600600</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>621485</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>599300</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>621013</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>93,23%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>91,5%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>94,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>911</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>636612</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>623220</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>648223</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>91,19%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1229970</t>
+          <t>1231256</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1263683</t>
+          <t>1264212</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,33%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>61540</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>49769</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>74357</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>44439</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>34891</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>55776</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>35363</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>57076</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>6,77%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>8,5%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>61540</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>49929</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>74932</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>8,81%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>90844</t>
+          <t>90315</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124557</t>
+          <t>123271</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>698152</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>698152</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>698152</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>656376</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>656376</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>656376</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>996</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>698152</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>698152</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>698152</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si sus dientes estan sanos en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si sus dientes están sanos en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>110611</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>104083</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>116075</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>90,02%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>84,7%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>94,46%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>103449</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>97320</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>108226</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>89,55%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>93,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>123076</t>
+          <t>106992</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114855</t>
+          <t>99952</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>129466</t>
+          <t>111779</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>226526</t>
+          <t>217602</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>216397</t>
+          <t>208261</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>234834</t>
+          <t>225618</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,02%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12268</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6804</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18796</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>9,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>15,3%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12066</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7289</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18195</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10,45%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>15,75%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13681</t>
+          <t>12669</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21902</t>
+          <t>19709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>25747</t>
+          <t>24938</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17439</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35876</t>
+          <t>34279</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122879</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122879</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122879</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>115515</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>115515</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>115515</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136757</t>
+          <t>119661</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136757</t>
+          <t>119661</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136757</t>
+          <t>119661</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>252273</t>
+          <t>242540</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>252273</t>
+          <t>242540</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>252273</t>
+          <t>242540</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>207421</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>196718</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>214517</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>89,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>84,81%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>92,49%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>250</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>173475</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>166911</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>178384</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>92,82%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>89,31%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>95,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>221689</t>
+          <t>168458</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>210549</t>
+          <t>160928</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229598</t>
+          <t>173273</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>395163</t>
+          <t>375880</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>382917</t>
+          <t>363057</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>405406</t>
+          <t>384956</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24518</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17422</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>35221</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>15,19%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>13423</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8514</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19987</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,18%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,69%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>26747</t>
+          <t>13210</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18838</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37887</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>40170</t>
+          <t>37728</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29927</t>
+          <t>28652</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52416</t>
+          <t>50551</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231939</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231939</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231939</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186898</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186898</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186898</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>248436</t>
+          <t>181668</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>248436</t>
+          <t>181668</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>248436</t>
+          <t>181668</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>435333</t>
+          <t>413608</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>435333</t>
+          <t>413608</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>435333</t>
+          <t>413608</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>148057</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>139568</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>154411</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>88,58%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>92,38%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>168763</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>159850</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>176982</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>89,77%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>85,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>94,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>163020</t>
+          <t>136397</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>153710</t>
+          <t>129042</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>169589</t>
+          <t>142275</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>331783</t>
+          <t>284454</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>319230</t>
+          <t>273079</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>342601</t>
+          <t>294077</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19224</t>
+          <t>19090</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11005</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28137</t>
+          <t>27579</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20683</t>
+          <t>18276</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14114</t>
+          <t>12398</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29993</t>
+          <t>25631</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>39907</t>
+          <t>37366</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29089</t>
+          <t>27743</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52460</t>
+          <t>48741</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167147</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167147</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167147</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>187987</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>187987</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>187987</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183703</t>
+          <t>154673</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183703</t>
+          <t>154673</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183703</t>
+          <t>154673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371690</t>
+          <t>321820</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371690</t>
+          <t>321820</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371690</t>
+          <t>321820</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>139366</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>129500</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>146696</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>83,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>77,73%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>88,05%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>130864</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>121252</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>139602</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>78,78%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>72,99%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>84,04%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>149306</t>
+          <t>129739</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>139765</t>
+          <t>119255</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>156770</t>
+          <t>138119</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>280171</t>
+          <t>269106</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>265955</t>
+          <t>257040</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>292670</t>
+          <t>281532</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27242</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19912</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>37108</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>11,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>22,27%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>35252</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>26514</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>44864</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>21,22%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15,96%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>27,01%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>28557</t>
+          <t>35432</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21093</t>
+          <t>27052</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38098</t>
+          <t>45916</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>63808</t>
+          <t>62673</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>51309</t>
+          <t>50247</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>78024</t>
+          <t>74739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166608</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166608</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166608</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>166116</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>166116</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>166116</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177863</t>
+          <t>165171</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177863</t>
+          <t>165171</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177863</t>
+          <t>165171</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>343979</t>
+          <t>331779</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>343979</t>
+          <t>331779</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>343979</t>
+          <t>331779</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>605456</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>588897</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>619965</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>87,93%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>85,52%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>90,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>804</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>576551</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>561769</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>591434</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>87,82%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>85,57%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>90,09%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>829</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>657092</t>
+          <t>541586</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>638033</t>
+          <t>526008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>672062</t>
+          <t>553879</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1233643</t>
+          <t>1147041</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1212458</t>
+          <t>1125379</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1257706</t>
+          <t>1165551</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>88,99%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>83118</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>68609</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>99677</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>14,48%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>79965</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>65082</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>94747</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>12,18%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>14,43%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>89667</t>
+          <t>79587</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74697</t>
+          <t>67294</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>108726</t>
+          <t>95165</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>169632</t>
+          <t>162705</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>145569</t>
+          <t>144195</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>190817</t>
+          <t>184367</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>688574</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>688574</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>688574</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>922</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>656516</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>656516</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>656516</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>746759</t>
+          <t>621173</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>746759</t>
+          <t>621173</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>746759</t>
+          <t>621173</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1403275</t>
+          <t>1309746</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1403275</t>
+          <t>1309746</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1403275</t>
+          <t>1309746</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
